--- a/jogos_2025-06-22.xlsx
+++ b/jogos_2025-06-22.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.75</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.37</v>
-      </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.88</v>
+        <v>2.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['5', '66']</t>
+          <t>['41', '74', '86']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['9', '81', '86']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45830.08333333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="Z5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['5', '66']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['9', '81', '86']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2</v>
       </c>
-      <c r="AA5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['41', '74', '86']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45830.08333333334</v>
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>2.97</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>12.67</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>3.74</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>2.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['10', '49']</t>
+          <t>['29', '3', '85']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '68', '90+4']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.95</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45830.29166666666</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,80 +1830,80 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>2.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.47</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Z11" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['83', '80']</t>
+          <t>['9', '33']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ11" t="n">
         <v>3.6</v>
@@ -1933,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>9.199999999999999</v>
+        <v>12.67</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="T12" t="n">
         <v>2.35</v>
@@ -1989,10 +1989,10 @@
         <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>4.2</v>
@@ -2001,23 +2001,23 @@
         <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AB12" t="n">
         <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['10', '49']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.74</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="T13" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['29', '3', '85']</t>
+          <t>['83', '80']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['31', '68', '90+4']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2181,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.95</v>
+        <v>7.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['56', '72']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['69', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,23 +2320,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.2</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.22</v>
       </c>
-      <c r="X15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AC15" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['6', '72']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['65', '9002']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>2.22</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['6', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['65', '9002']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.85</v>
+        <v>2.13</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2697,35 +2697,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Binh Dinh</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.99</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>4.25</v>
+        <v>3.63</v>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.28</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['81', '73']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['24', '43', '39', '45+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2826,32 +2826,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
         <v>2.9</v>
       </c>
       <c r="P19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45830.29166666666</v>
@@ -2955,119 +2955,119 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.51</v>
-      </c>
       <c r="Q20" t="n">
-        <v>8.449999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['56', '72']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['69', '78']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['9', '33']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45830.29166666666</v>
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Binh Dinh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['81', '73']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '43', '39', '45+2']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45830.29166666666</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.83</v>
+        <v>3.41</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
@@ -3789,10 +3789,10 @@
         <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
         <v>1.05</v>
@@ -3801,47 +3801,47 @@
         <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['43', '4502']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['5', '9010']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45830.41666666666</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="R27" t="n">
         <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
         <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
         <v>1.53</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['9005']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45830.41666666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="N28" t="n">
-        <v>4.39</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
         <v>3.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '4502']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['5', '9010']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45830.41666666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4215,20 +4215,20 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45830.41666666666</v>
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.93</v>
+        <v>3.62</v>
       </c>
       <c r="N30" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['18', '88']</t>
+          <t>['17', '88']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,19 +4384,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="M31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S31" t="n">
         <v>3.8</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.61</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['32', '48']</t>
+          <t>['28', '77']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45830.45833333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>1.66</v>
+        <v>6.6</v>
       </c>
       <c r="O32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q32" t="n">
         <v>5.5</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['11', '15', '22', '45+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.13</v>
+        <v>2.63</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.76</v>
+        <v>1.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.49</v>
+        <v>3.6</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45830.45833333334</v>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,49 +4668,49 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.22</v>
+        <v>5.4</v>
       </c>
       <c r="M33" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>9.4</v>
+        <v>1.46</v>
       </c>
       <c r="O33" t="n">
-        <v>1.47</v>
+        <v>5.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.8</v>
+        <v>1.81</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
         <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AA33" t="n">
         <v>2.05</v>
@@ -4719,26 +4719,26 @@
         <v>1.61</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['28', '77']</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['48', '52']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>3.96</v>
       </c>
       <c r="N34" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="O34" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['48', '52']</t>
+          <t>['11', '15', '22', '45+2']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45830.45833333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>6.6</v>
+        <v>1.64</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>1.37</v>
+        <v>4.4</v>
       </c>
       <c r="O35" t="n">
-        <v>5.4</v>
+        <v>2.19</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.98</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="U35" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X35" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['1', '36']</t>
+          <t>['32', '48']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['26', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG35" t="n">
         <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.11</v>
+        <v>2.15</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.5</v>
+        <v>1.49</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.38</v>
+        <v>2.7</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45830.45833333334</v>
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>6.6</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>1.37</v>
       </c>
       <c r="O36" t="n">
-        <v>2.05</v>
+        <v>5.4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.38</v>
+        <v>1.98</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="U36" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.28</v>
+        <v>2.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['40', '75']</t>
+          <t>['1', '36']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['26', '88']</t>
         </is>
       </c>
       <c r="AG36" t="n">
         <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.51</v>
+        <v>3.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.52</v>
+        <v>1.38</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45830.45833333334</v>
@@ -5158,19 +5158,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="P37" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.5</v>
+        <v>4.38</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="U37" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AA37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['40', '75']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45830.45833333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="M38" t="n">
-        <v>9</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>31</v>
+        <v>2.26</v>
       </c>
       <c r="O38" t="n">
-        <v>1.32</v>
+        <v>3.8</v>
       </c>
       <c r="P38" t="n">
-        <v>3.26</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>2.94</v>
       </c>
       <c r="R38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.2</v>
       </c>
-      <c r="S38" t="n">
-        <v>4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC38" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['23', '90']</t>
+          <t>['45+2', '66']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45830.5</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" t="n">
         <v>1</v>
       </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="O39" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X39" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.72</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['21', '33', '35', '84']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['26', '78']</t>
+          <t>['4503']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.1</v>
+        <v>1.21</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45830.5</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,19 +5545,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.46</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="N40" t="n">
-        <v>2.03</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="P40" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U40" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X40" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD40" t="n">
         <v>2.05</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
+          <t>['53', '59', '70', '82', '9002']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
       <c r="AG40" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45830.5</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.56</v>
+        <v>1.06</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>31</v>
       </c>
       <c r="O41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>15</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.1</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U41" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
-        <v>4.33</v>
+        <v>5.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.22</v>
+        <v>2.51</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['23', '90']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45830.5</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
         <v>3</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>6.5</v>
+        <v>2.02</v>
       </c>
       <c r="O42" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="P42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.27</v>
+        <v>3.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['8', '58', '86']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '26', '47']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.9</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.29</v>
+        <v>2.38</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45830.5</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,23 +5932,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>1</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="M43" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N43" t="n">
+        <v>11</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S43" t="n">
         <v>3.3</v>
       </c>
-      <c r="N43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.78</v>
-      </c>
       <c r="T43" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC43" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD43" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['86', '90+3']</t>
+          <t>['17', '90+5']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>1</v>
       </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.16</v>
+        <v>3.46</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="N44" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O44" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T44" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V44" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.28</v>
       </c>
-      <c r="X44" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD44" t="n">
         <v>2.05</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['21', '26', '47']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45830.5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,109 +6190,109 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['21', '33', '35', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['4503']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45830.5</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
         <v>2</v>
       </c>
-      <c r="H46" t="n">
-        <v>3</v>
-      </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>3.71</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T46" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['78', '85']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['33', '77', '81']</t>
+          <t>['26', '78']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45830.5</v>
@@ -6448,109 +6448,109 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>7</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X47" t="n">
         <v>5</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="Y47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['8', '58', '86']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH47" t="n">
         <v>2.9</v>
       </c>
-      <c r="O47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q47" t="n">
+      <c r="AI47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>3.75</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['53', '59', '70', '82', '9002']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45830.5</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,16 +6577,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.35</v>
+        <v>1.56</v>
       </c>
       <c r="M48" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="N48" t="n">
-        <v>2.26</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="P48" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB48" t="n">
         <v>1.5</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC48" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['45+2', '66']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45830.5</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,91 +6706,91 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['17', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6835,20 +6835,20 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
         <v>1</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.62</v>
+        <v>2.66</v>
       </c>
       <c r="M50" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>4.53</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="P50" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S50" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T50" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W50" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="X50" t="n">
-        <v>4.11</v>
+        <v>3.3</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AD50" t="n">
         <v>2</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['86', '9003']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45830.5</v>
@@ -6973,94 +6973,94 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N51" t="n">
-        <v>5.23</v>
+        <v>6.2</v>
       </c>
       <c r="O51" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
+          <t>['4501', '55']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7093,25 +7093,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,49 +7119,49 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="N52" t="n">
-        <v>6.76</v>
+        <v>2.72</v>
       </c>
       <c r="O52" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="S52" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T52" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="U52" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V52" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W52" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="X52" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AA52" t="n">
         <v>5.25</v>
@@ -7170,10 +7170,10 @@
         <v>1.13</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['37', '82']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI52" t="n">
         <v>2.3</v>
       </c>
-      <c r="AI52" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45830.54861111111</v>
@@ -7222,75 +7222,75 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="M53" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>6.76</v>
       </c>
       <c r="O53" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="P53" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S53" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T53" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="U53" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V53" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W53" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="X53" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AA53" t="n">
         <v>5.25</v>
@@ -7299,10 +7299,10 @@
         <v>1.13</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7311,20 +7311,20 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['37', '82']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45830.54861111111</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,19 +7738,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45830.58333333334</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,19 +7867,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['90+7']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45830.58333333334</v>
@@ -8263,94 +8263,94 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['31', '67', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['27', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8631,29 +8631,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="M64" t="n">
-        <v>3.23</v>
+        <v>2.54</v>
       </c>
       <c r="N64" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="O64" t="n">
-        <v>2.65</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ64" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['38', '49']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>2.45</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45830.64583333334</v>
@@ -8760,32 +8760,32 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.32</v>
+        <v>2.34</v>
       </c>
       <c r="M65" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>8</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U65" t="n">
+      <c r="AB65" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>['38', '49']</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
         <v>1.27</v>
       </c>
-      <c r="V65" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH65" t="n">
-        <v>2.9</v>
+        <v>1.74</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="AJ65" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45830.64583333334</v>
@@ -8899,25 +8899,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="M66" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="N66" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="R66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W66" t="n">
         <v>1.6</v>
       </c>
-      <c r="S66" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T66" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.65</v>
-      </c>
       <c r="X66" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Y66" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AA66" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AB66" t="n">
         <v>1.1</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AI66" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45830.64583333334</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9046,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.45</v>
+        <v>1.32</v>
       </c>
       <c r="M67" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="N67" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>8</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC67" t="n">
         <v>3</v>
       </c>
-      <c r="O67" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X67" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AD67" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="AJ67" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45830.64583333334</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,109 +9157,109 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
         <v>1</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X68" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD68" t="n">
         <v>2</v>
       </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M68" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N68" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O68" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S68" t="n">
-        <v>4</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X68" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['66', '88']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['49', '60']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="AI68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ68" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45830.66666666666</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,19 +9286,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="M69" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="N69" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X69" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z69" t="n">
         <v>2.88</v>
       </c>
-      <c r="O69" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T69" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W69" t="n">
+      <c r="AA69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC69" t="n">
         <v>1.4</v>
       </c>
-      <c r="X69" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z69" t="n">
+      <c r="AD69" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>['49', '60']</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI69" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA69" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45830.66666666666</v>
@@ -9415,22 +9415,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
@@ -9441,83 +9441,83 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M70" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="N70" t="n">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="O70" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="P70" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.3</v>
+        <v>3.86</v>
       </c>
       <c r="R70" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI70" t="n">
         <v>1.82</v>
       </c>
-      <c r="S70" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T70" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X70" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>['69', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>['5', '62']</t>
-        </is>
-      </c>
-      <c r="AG70" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ70" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45830.66666666666</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,23 +9544,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
         <v>1</v>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
@@ -9570,83 +9570,83 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.7</v>
+        <v>2.19</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="N71" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="O71" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="P71" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X71" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
         <v>1.36</v>
       </c>
-      <c r="S71" t="n">
-        <v>3</v>
-      </c>
-      <c r="T71" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U71" t="n">
+      <c r="AH71" t="n">
         <v>1.4</v>
       </c>
-      <c r="V71" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X71" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>['66', '88']</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI71" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45830.66666666666</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,25 +9673,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G72" t="n">
         <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9699,80 +9699,80 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W72" t="n">
         <v>1.77</v>
       </c>
-      <c r="M72" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N72" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O72" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T72" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.53</v>
-      </c>
       <c r="X72" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AA72" t="n">
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['88', '90+8']</t>
+          <t>['69', '90+1']</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '62']</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AI72" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ72" t="n">
         <v>3</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="M73" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="N73" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="O73" t="n">
-        <v>2.98</v>
+        <v>2.58</v>
       </c>
       <c r="P73" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.86</v>
+        <v>4.55</v>
       </c>
       <c r="R73" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="S73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X73" t="n">
         <v>2.25</v>
       </c>
-      <c r="T73" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V73" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2.26</v>
-      </c>
       <c r="Y73" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA73" t="n">
-        <v>6.25</v>
+        <v>5.2</v>
       </c>
       <c r="AB73" t="n">
         <v>1.13</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['88', '90+8']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45830.66666666666</v>
@@ -10060,19 +10060,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -10086,61 +10086,61 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.26</v>
+        <v>2.65</v>
       </c>
       <c r="M75" t="n">
-        <v>3.63</v>
+        <v>4.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="O75" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P75" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="R75" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S75" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="T75" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="U75" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="V75" t="n">
         <v>1.01</v>
       </c>
       <c r="W75" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X75" t="n">
-        <v>5.7</v>
+        <v>6.46</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -10149,20 +10149,20 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>['29', '69']</t>
+          <t>['42', '53', '51']</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI75" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AJ75" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45830.67708333334</v>
@@ -10189,19 +10189,19 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.65</v>
+        <v>3.26</v>
       </c>
       <c r="M76" t="n">
-        <v>4.01</v>
+        <v>3.63</v>
       </c>
       <c r="N76" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="O76" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P76" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="R76" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S76" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="T76" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="U76" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="V76" t="n">
         <v>1.01</v>
       </c>
       <c r="W76" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X76" t="n">
-        <v>6.46</v>
+        <v>5.7</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z76" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AD76" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10278,20 +10278,20 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['42', '53', '51']</t>
+          <t>['29', '69']</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45830.67708333334</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,109 +10318,109 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['12', '51']</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['55', '60']</t>
+          <t>['14', '89', '90+9']</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45830.70833333334</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,109 +10576,109 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
         <v>1</v>
       </c>
-      <c r="H79" t="n">
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O79" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>['12', '51']</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>['55', '60']</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ79" t="n">
         <v>3</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>['14', '89', '90+9']</t>
-        </is>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
         <v>45830.70833333334</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,25 +11221,25 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -11247,83 +11247,83 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>['12', '84', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['64', '67', '75', '89', '90+1']</t>
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
         <v>45830.83333333334</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,109 +11350,109 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X85" t="n">
         <v>5</v>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '84', '90+2']</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>['64', '67', '75', '89', '90+1']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK85" s="3" t="n">
         <v>45830.83333333334</v>
